--- a/HTDW_4438/urdf/initial.xlsx
+++ b/HTDW_4438/urdf/initial.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="305">
   <si>
     <t>base_link 的质量属性</t>
   </si>
@@ -152,13 +152,13 @@
     <t>质量 = 0.27079698 千克</t>
   </si>
   <si>
-    <t>质量 = 0.47279447 千克</t>
+    <t>质量 = 0.48086181 千克</t>
   </si>
   <si>
     <t>重心和惯性张量的输出是以 总装 为坐标系。</t>
   </si>
   <si>
-    <t>质量 = 0.47279491 千克</t>
+    <t>质量 = 0.48086142 千克</t>
   </si>
   <si>
     <t>质量 = 0.06068055 千克</t>
@@ -173,7 +173,7 @@
     <t>体积 = 0.00004337 立方米</t>
   </si>
   <si>
-    <t>体积 = 0.00011084 立方米</t>
+    <t>体积 = 0.00011383 立方米</t>
   </si>
   <si>
     <t>体积 = 0.00005567 立方米</t>
@@ -188,10 +188,10 @@
     <t>表面积 = 0.04433507 平方米</t>
   </si>
   <si>
-    <t>表面积 = 0.09679875 平方米</t>
-  </si>
-  <si>
-    <t>表面积 = 0.09679861 平方米</t>
+    <t>表面积 = 0.09677225 平方米</t>
+  </si>
+  <si>
+    <t>表面积 = 0.09677224 平方米</t>
   </si>
   <si>
     <t>表面积 = 0.01633342 平方米</t>
@@ -209,16 +209,19 @@
     <t>X = -0.00266064</t>
   </si>
   <si>
-    <t>X = -0.00297476</t>
-  </si>
-  <si>
-    <t>X = -0.00313741</t>
+    <t>X = -0.00360471</t>
+  </si>
+  <si>
+    <t>X = -0.00559051</t>
   </si>
   <si>
     <t>X = 0.00266064</t>
   </si>
   <si>
-    <t>X = -0.00325860</t>
+    <t>X = -0.00555466</t>
+  </si>
+  <si>
+    <t>X = -0.00521957</t>
   </si>
   <si>
     <t>Y = 0.00204115</t>
@@ -227,7 +230,7 @@
     <t>Y = 0.00153194</t>
   </si>
   <si>
-    <t>Y = -0.01800033</t>
+    <t>Y = -0.01763227</t>
   </si>
   <si>
     <t>X = 0.01005013</t>
@@ -239,19 +242,22 @@
     <t>Y = -0.00153194</t>
   </si>
   <si>
-    <t>Y = 0.01800027</t>
+    <t>Y = 0.01763224</t>
   </si>
   <si>
     <t>X = 0.01005014</t>
   </si>
   <si>
+    <t>Y = 0.01761785</t>
+  </si>
+  <si>
     <t>Z = -0.00063500</t>
   </si>
   <si>
     <t>Z = -0.00011724</t>
   </si>
   <si>
-    <t>Z = -0.02107619</t>
+    <t>Z = -0.02190343</t>
   </si>
   <si>
     <t>Y = 0.00000313</t>
@@ -263,10 +269,13 @@
     <t>Z = 0.00011724</t>
   </si>
   <si>
-    <t>Z = -0.02121661</t>
-  </si>
-  <si>
-    <t>Z = -0.02118103</t>
+    <t>Z = -0.02107369</t>
+  </si>
+  <si>
+    <t>Z = -0.02101551</t>
+  </si>
+  <si>
+    <t>Z = -0.02116423</t>
   </si>
   <si>
     <t>Z = -0.05890115</t>
@@ -296,34 +305,37 @@
     <t>Px = 0.00002353</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ix = ( 0.08898200, -0.23603912,  0.96766096)   </t>
-  </si>
-  <si>
-    <t>Px = 0.00018980</t>
+    <t xml:space="preserve"> Ix = ( 0.10684996, -0.24410959,  0.96384314)   </t>
+  </si>
+  <si>
+    <t>Px = 0.00019192</t>
   </si>
   <si>
     <t xml:space="preserve"> Ix = ( 0.99698254, -0.07664407,  0.01230872)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Ix = ( 0.08611770,  0.23574777,  0.96799108)   </t>
-  </si>
-  <si>
-    <t>Px = 0.00019031</t>
+    <t xml:space="preserve"> Ix = ( 0.19950702,  0.23599699,  0.95105330)   </t>
+  </si>
+  <si>
+    <t>Px = 0.00019477</t>
   </si>
   <si>
     <t xml:space="preserve"> Ix = ( 0.99698254, -0.07664407, -0.01230872)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Ix = ( 0.08462740, -0.23831641,  0.96749341)   </t>
-  </si>
-  <si>
-    <t>Px = 0.00019058</t>
+    <t xml:space="preserve"> Ix = ( 0.19030401, -0.23770677,  0.95251240)   </t>
+  </si>
+  <si>
+    <t>Px = 0.00019482</t>
   </si>
   <si>
     <t xml:space="preserve"> Ix = ( 0.99698254,  0.07664407,  0.01230872)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Ix = ( 0.08611769,  0.23574777,  0.96799108)   </t>
+    <t xml:space="preserve"> Ix = ( 0.18681294,  0.23703120,  0.95337146)   </t>
+  </si>
+  <si>
+    <t>Px = 0.00019474</t>
   </si>
   <si>
     <t xml:space="preserve"> Iy = ( 0.06976381,  0.99751104,  0.01023372)   </t>
@@ -338,10 +350,10 @@
     <t>Py = 0.00003439</t>
   </si>
   <si>
-    <t xml:space="preserve"> Iy = ( 0.12106935, -0.96174793, -0.24572980)   </t>
-  </si>
-  <si>
-    <t>Py = 0.00098467</t>
+    <t xml:space="preserve"> Iy = ( 0.13376419, -0.95705066, -0.25721814)   </t>
+  </si>
+  <si>
+    <t>Py = 0.00099049</t>
   </si>
   <si>
     <t xml:space="preserve"> Ix = (-0.07024785,  0.00008815,  0.99752956)   </t>
@@ -359,25 +371,28 @@
     <t xml:space="preserve"> Iy = ( 0.07627701,  0.99669508,  0.02794148)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Iy = (-0.14962684, -0.95752023,  0.24650927)   </t>
-  </si>
-  <si>
-    <t>Py = 0.00098055</t>
+    <t xml:space="preserve"> Iy = (-0.09755622, -0.96095953,  0.25891998)   </t>
+  </si>
+  <si>
+    <t>Py = 0.00099604</t>
   </si>
   <si>
     <t xml:space="preserve"> Iy = ( 0.07627701,  0.99669508, -0.02794148)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Iy = ( 0.17950634, -0.95144374, -0.25006456)   </t>
-  </si>
-  <si>
-    <t>Py = 0.00098135</t>
+    <t xml:space="preserve"> Iy = ( 0.12910136, -0.95575783, -0.26431006)   </t>
+  </si>
+  <si>
+    <t>Py = 0.00099763</t>
   </si>
   <si>
     <t xml:space="preserve"> Iy = (-0.07627701,  0.99669508, -0.02794148)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Iy = (-0.14962691, -0.95752022,  0.24650927)   </t>
+    <t xml:space="preserve"> Iy = (-0.08720558, -0.96262363,  0.25641943)   </t>
+  </si>
+  <si>
+    <t>Py = 0.00099679</t>
   </si>
   <si>
     <t xml:space="preserve"> Iz = ( 0.00381364, -0.01052533,  0.99993733)   </t>
@@ -392,10 +407,10 @@
     <t>Pz = 0.00003580</t>
   </si>
   <si>
-    <t xml:space="preserve"> Iz = ( 0.98864777,  0.13901961, -0.05700115)   </t>
-  </si>
-  <si>
-    <t>Pz = 0.00103935</t>
+    <t xml:space="preserve"> Iz = ( 0.98523613,  0.15641144, -0.06960770)   </t>
+  </si>
+  <si>
+    <t>Pz = 0.00104575</t>
   </si>
   <si>
     <t xml:space="preserve"> Iy = ( 0.99752954, -0.00025024,  0.07024787)   </t>
@@ -413,25 +428,28 @@
     <t xml:space="preserve"> Iz = (-0.01440959, -0.02691830,  0.99953378)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Iz = ( 0.98498505, -0.16606626, -0.04718524)   </t>
-  </si>
-  <si>
-    <t>Pz = 0.00103643</t>
+    <t xml:space="preserve"> Iz = ( 0.97502807, -0.14443752, -0.16869519)   </t>
+  </si>
+  <si>
+    <t>Pz = 0.00105408</t>
   </si>
   <si>
     <t xml:space="preserve"> Iz = ( 0.01440959,  0.02691830,  0.99953378)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Iz = ( 0.98011003,  0.19483351, -0.03773891)   </t>
-  </si>
-  <si>
-    <t>Pz = 0.00103604</t>
+    <t xml:space="preserve"> Iz = ( 0.97319948,  0.17326991, -0.15119628)   </t>
+  </si>
+  <si>
+    <t>Pz = 0.00105519</t>
   </si>
   <si>
     <t xml:space="preserve"> Iz = (-0.01440959,  0.02691830,  0.99953378)   </t>
   </si>
   <si>
-    <t xml:space="preserve"> Iz = ( 0.98498504, -0.16606632, -0.04718522)   </t>
+    <t xml:space="preserve"> Iz = ( 0.97851730, -0.13104178, -0.15916011)   </t>
+  </si>
+  <si>
+    <t>Pz = 0.00105422</t>
   </si>
   <si>
     <t xml:space="preserve"> Iz = ( 0.00025581,  0.99999996, -0.00007035)   </t>
@@ -470,13 +488,13 @@
     <t>Lxz = 0.00000015</t>
   </si>
   <si>
-    <t>Lxx = 0.00103183</t>
-  </si>
-  <si>
-    <t>Lxy = 0.00002421</t>
-  </si>
-  <si>
-    <t>Lxz = -0.00007152</t>
+    <t>Lxx = 0.00103502</t>
+  </si>
+  <si>
+    <t>Lxy = 0.00002935</t>
+  </si>
+  <si>
+    <t>Lxz = -0.00008603</t>
   </si>
   <si>
     <t>Lxy = 0.00000083</t>
@@ -485,22 +503,31 @@
     <t>Lxz = -0.00000015</t>
   </si>
   <si>
-    <t>Lxx = 0.00102890</t>
-  </si>
-  <si>
-    <t>Lxy = -0.00002518</t>
-  </si>
-  <si>
-    <t>Lxz = -0.00006847</t>
-  </si>
-  <si>
-    <t>Lxx = 0.00102822</t>
-  </si>
-  <si>
-    <t>Lxy = 0.00002639</t>
-  </si>
-  <si>
-    <t>Lxz = -0.00006677</t>
+    <t>Lxx = 0.00101933</t>
+  </si>
+  <si>
+    <t>Lxy = -0.00004590</t>
+  </si>
+  <si>
+    <t>Lxz = -0.00016158</t>
+  </si>
+  <si>
+    <t>Lxx = 0.00102307</t>
+  </si>
+  <si>
+    <t>Lxy = 0.00004602</t>
+  </si>
+  <si>
+    <t>Lxz = -0.00015399</t>
+  </si>
+  <si>
+    <t>Lxx = 0.00102378</t>
+  </si>
+  <si>
+    <t>Lxy = -0.00004288</t>
+  </si>
+  <si>
+    <t>Lxz = -0.00015179</t>
   </si>
   <si>
     <t>Lyx = 0.00048912</t>
@@ -521,13 +548,13 @@
     <t>Lyz = -0.00000003</t>
   </si>
   <si>
-    <t>Lyx = 0.00002421</t>
-  </si>
-  <si>
-    <t>Lyy = 0.00094144</t>
-  </si>
-  <si>
-    <t>Lyz = 0.00018112</t>
+    <t>Lyx = 0.00002935</t>
+  </si>
+  <si>
+    <t>Lyy = 0.00094426</t>
+  </si>
+  <si>
+    <t>Lyz = 0.00018729</t>
   </si>
   <si>
     <t>Lxx = 0.00021231</t>
@@ -548,25 +575,34 @@
     <t>Lyx = 0.00000083</t>
   </si>
   <si>
-    <t>Lyx = -0.00002518</t>
-  </si>
-  <si>
-    <t>Lyy = 0.00093817</t>
-  </si>
-  <si>
-    <t>Lyz = -0.00017990</t>
+    <t>Lyx = -0.00004590</t>
+  </si>
+  <si>
+    <t>Lyy = 0.00095262</t>
+  </si>
+  <si>
+    <t>Lyz = -0.00017843</t>
   </si>
   <si>
     <t>Lyz = 0.00000003</t>
   </si>
   <si>
-    <t>Lyx = 0.00002639</t>
-  </si>
-  <si>
-    <t>Lyy = 0.00093851</t>
-  </si>
-  <si>
-    <t>Lyz = 0.00018193</t>
+    <t>Lyx = 0.00004602</t>
+  </si>
+  <si>
+    <t>Lyy = 0.00095399</t>
+  </si>
+  <si>
+    <t>Lyz = 0.00018026</t>
+  </si>
+  <si>
+    <t>Lyx = -0.00004288</t>
+  </si>
+  <si>
+    <t>Lyy = 0.00095271</t>
+  </si>
+  <si>
+    <t>Lyz = -0.00018005</t>
   </si>
   <si>
     <t>Lzx = 0.00004378</t>
@@ -587,13 +623,13 @@
     <t>Lzz = 0.00003580</t>
   </si>
   <si>
-    <t>Lzx = -0.00007152</t>
-  </si>
-  <si>
-    <t>Lzy = 0.00018112</t>
-  </si>
-  <si>
-    <t>Lzz = 0.00024056</t>
+    <t>Lzx = -0.00008603</t>
+  </si>
+  <si>
+    <t>Lzy = 0.00018729</t>
+  </si>
+  <si>
+    <t>Lzz = 0.00024889</t>
   </si>
   <si>
     <t>Lyx = 0.00000000</t>
@@ -614,25 +650,34 @@
     <t>Lzx = -0.00000015</t>
   </si>
   <si>
-    <t>Lzx = -0.00006847</t>
-  </si>
-  <si>
-    <t>Lzy = -0.00017990</t>
-  </si>
-  <si>
-    <t>Lzz = 0.00024021</t>
+    <t>Lzx = -0.00016158</t>
+  </si>
+  <si>
+    <t>Lzy = -0.00017843</t>
+  </si>
+  <si>
+    <t>Lzz = 0.00027294</t>
   </si>
   <si>
     <t>Lzy = 0.00000003</t>
   </si>
   <si>
-    <t>Lzx = -0.00006677</t>
-  </si>
-  <si>
-    <t>Lzy = 0.00018193</t>
-  </si>
-  <si>
-    <t>Lzz = 0.00024123</t>
+    <t>Lzx = -0.00015399</t>
+  </si>
+  <si>
+    <t>Lzy = 0.00018026</t>
+  </si>
+  <si>
+    <t>Lzz = 0.00027057</t>
+  </si>
+  <si>
+    <t>Lzx = -0.00015179</t>
+  </si>
+  <si>
+    <t>Lzy = -0.00018005</t>
+  </si>
+  <si>
+    <t>Lzz = 0.00026924</t>
   </si>
   <si>
     <t>Lzx = 0.00001460</t>
@@ -674,13 +719,13 @@
     <t>Ixz = 0.00000007</t>
   </si>
   <si>
-    <t>Ixx = 0.00139504</t>
-  </si>
-  <si>
-    <t>Ixy = -0.00000111</t>
-  </si>
-  <si>
-    <t>Ixz = -0.00010117</t>
+    <t>Ixx = 0.00141521</t>
+  </si>
+  <si>
+    <t>Ixy = -0.00000122</t>
+  </si>
+  <si>
+    <t>Ixz = -0.00012400</t>
   </si>
   <si>
     <t>Ixy = -0.00000027</t>
@@ -689,22 +734,31 @@
     <t>Ixz = -0.00000007</t>
   </si>
   <si>
-    <t>Ixx = 0.00139492</t>
-  </si>
-  <si>
-    <t>Ixy = 0.00000152</t>
-  </si>
-  <si>
-    <t>Ixz = -0.00009994</t>
-  </si>
-  <si>
-    <t>Ixx = 0.00139353</t>
-  </si>
-  <si>
-    <t>Ixy = -0.00000134</t>
-  </si>
-  <si>
-    <t>Ixz = -0.00009940</t>
+    <t>Ixx = 0.00138238</t>
+  </si>
+  <si>
+    <t>Ixy = 0.00000150</t>
+  </si>
+  <si>
+    <t>Ixz = -0.00021823</t>
+  </si>
+  <si>
+    <t>Ixx = 0.00138494</t>
+  </si>
+  <si>
+    <t>Ixy = -0.00000107</t>
+  </si>
+  <si>
+    <t>Ixz = -0.00021013</t>
+  </si>
+  <si>
+    <t>Ixx = 0.00138843</t>
+  </si>
+  <si>
+    <t>Ixy = 0.00000134</t>
+  </si>
+  <si>
+    <t>Ixz = -0.00020491</t>
   </si>
   <si>
     <t>Iyx = 0.00050600</t>
@@ -725,13 +779,13 @@
     <t>Iyz = 0.00000002</t>
   </si>
   <si>
-    <t>Iyx = -0.00000111</t>
-  </si>
-  <si>
-    <t>Iyy = 0.00115565</t>
-  </si>
-  <si>
-    <t>Iyz = 0.00000175</t>
+    <t>Iyx = -0.00000122</t>
+  </si>
+  <si>
+    <t>Iyy = 0.00118120</t>
+  </si>
+  <si>
+    <t>Iyz = 0.00000158</t>
   </si>
   <si>
     <t>Ixx = 0.00042283</t>
@@ -752,19 +806,25 @@
     <t>Iyx = -0.00000027</t>
   </si>
   <si>
-    <t>Iyx = 0.00000152</t>
-  </si>
-  <si>
-    <t>Iyz = 0.00000067</t>
+    <t>Iyx = 0.00000150</t>
+  </si>
+  <si>
+    <t>Iyz = 0.00000025</t>
   </si>
   <si>
     <t>Iyz = -0.00000002</t>
   </si>
   <si>
-    <t>Iyx = -0.00000134</t>
-  </si>
-  <si>
-    <t>Iyz = 0.00000166</t>
+    <t>Iyx = -0.00000107</t>
+  </si>
+  <si>
+    <t>Iyz = 0.00000208</t>
+  </si>
+  <si>
+    <t>Iyx = 0.00000134</t>
+  </si>
+  <si>
+    <t>Iyz = -0.00000075</t>
   </si>
   <si>
     <t>Izx = 0.00003853</t>
@@ -785,13 +845,13 @@
     <t>Izz = 0.00003835</t>
   </si>
   <si>
-    <t>Izx = -0.00010117</t>
-  </si>
-  <si>
-    <t>Izy = 0.00000175</t>
-  </si>
-  <si>
-    <t>Izz = 0.00039794</t>
+    <t>Izx = -0.00012400</t>
+  </si>
+  <si>
+    <t>Izy = 0.00000158</t>
+  </si>
+  <si>
+    <t>Izz = 0.00040463</t>
   </si>
   <si>
     <t>Iyx = 0.00000000</t>
@@ -809,25 +869,34 @@
     <t>Izx = -0.00000007</t>
   </si>
   <si>
-    <t>Izx = -0.00009994</t>
-  </si>
-  <si>
-    <t>Izy = 0.00000067</t>
-  </si>
-  <si>
-    <t>Izz = 0.00039806</t>
+    <t>Izx = -0.00021823</t>
+  </si>
+  <si>
+    <t>Izy = 0.00000025</t>
+  </si>
+  <si>
+    <t>Izz = 0.00043747</t>
   </si>
   <si>
     <t>Izy = -0.00000002</t>
   </si>
   <si>
-    <t>Izx = -0.00009940</t>
-  </si>
-  <si>
-    <t>Izy = 0.00000166</t>
-  </si>
-  <si>
-    <t>Izz = 0.00039944</t>
+    <t>Izx = -0.00021013</t>
+  </si>
+  <si>
+    <t>Izy = 0.00000208</t>
+  </si>
+  <si>
+    <t>Izz = 0.00043490</t>
+  </si>
+  <si>
+    <t>Izx = -0.00020491</t>
+  </si>
+  <si>
+    <t>Izy = -0.00000075</t>
+  </si>
+  <si>
+    <t>Izz = 0.00043160</t>
   </si>
   <si>
     <t>Izx = 0.00005052</t>
@@ -2514,7 +2583,7 @@
         <v>62</v>
       </c>
       <c r="CH12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="CM12" t="s">
         <v>57</v>
@@ -2525,1821 +2594,1812 @@
     </row>
     <row r="13" spans="1:98">
       <c r="B13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
+        <v>67</v>
+      </c>
+      <c r="T13" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>69</v>
+      </c>
+      <c r="BD13" t="s">
         <v>66</v>
       </c>
-      <c r="T13" t="s">
+      <c r="BJ13" t="s">
         <v>67</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="BP13" t="s">
         <v>68</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="BV13" t="s">
         <v>69</v>
       </c>
-      <c r="AL13" t="s">
+      <c r="CB13" t="s">
         <v>70</v>
       </c>
-      <c r="AR13" t="s">
-        <v>71</v>
-      </c>
-      <c r="AX13" t="s">
+      <c r="CH13" t="s">
+        <v>73</v>
+      </c>
+      <c r="CN13" t="s">
         <v>68</v>
       </c>
-      <c r="BD13" t="s">
-        <v>65</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP13" t="s">
-        <v>67</v>
-      </c>
-      <c r="BV13" t="s">
-        <v>68</v>
-      </c>
-      <c r="CB13" t="s">
+      <c r="CT13" t="s">
         <v>69</v>
-      </c>
-      <c r="CH13" t="s">
-        <v>70</v>
-      </c>
-      <c r="CN13" t="s">
-        <v>67</v>
-      </c>
-      <c r="CT13" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:98">
       <c r="B14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>78</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>81</v>
+      </c>
+      <c r="BP14" t="s">
+        <v>77</v>
+      </c>
+      <c r="BV14" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB14" t="s">
         <v>75</v>
       </c>
-      <c r="Z14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF14" t="s">
+      <c r="CH14" t="s">
+        <v>82</v>
+      </c>
+      <c r="CN14" t="s">
         <v>77</v>
       </c>
-      <c r="AL14" t="s">
+      <c r="CT14" t="s">
         <v>78</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>76</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BV14" t="s">
-        <v>76</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>73</v>
-      </c>
-      <c r="CH14" t="s">
-        <v>78</v>
-      </c>
-      <c r="CN14" t="s">
-        <v>75</v>
-      </c>
-      <c r="CT14" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:98">
       <c r="T15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Z15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AR15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AX15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="BP15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="BV15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="CN15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="CT15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:98">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AE16" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF16"/>
+        <v>86</v>
+      </c>
       <c r="AK16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="BC16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="BI16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="CA16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="CG16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:100">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Y17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AE17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AK17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AQ17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AW17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="BC17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="BI17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="BO17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="BU17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="CA17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="CG17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="CM17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="CS17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:100">
       <c r="B18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" t="s">
+        <v>91</v>
+      </c>
+      <c r="N18" t="s">
+        <v>92</v>
+      </c>
+      <c r="O18" t="s">
+        <v>93</v>
+      </c>
+      <c r="S18" t="s">
         <v>87</v>
       </c>
-      <c r="I18" t="s">
-        <v>88</v>
-      </c>
-      <c r="N18" t="s">
-        <v>89</v>
-      </c>
-      <c r="O18" t="s">
-        <v>90</v>
-      </c>
-      <c r="S18" t="s">
-        <v>84</v>
-      </c>
       <c r="Y18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AF18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG18" t="s">
         <v>91</v>
       </c>
-      <c r="AG18" t="s">
-        <v>88</v>
-      </c>
       <c r="AL18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AM18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AQ18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="BD18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="BE18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="BJ18" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="BK18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="BO18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="BU18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="CB18" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="CC18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="CH18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="CI18" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="CM18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="CS18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:100">
       <c r="B19" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="T19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="U19" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG19" t="s">
         <v>106</v>
       </c>
-      <c r="Z19" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF19" t="s">
+      <c r="AL19" t="s">
+        <v>114</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR19" t="s">
         <v>109</v>
       </c>
-      <c r="AG19" t="s">
-        <v>102</v>
-      </c>
-      <c r="AL19" t="s">
+      <c r="AS19" t="s">
         <v>110</v>
       </c>
-      <c r="AM19" t="s">
+      <c r="AX19" t="s">
         <v>111</v>
       </c>
-      <c r="AR19" t="s">
-        <v>105</v>
-      </c>
-      <c r="AS19" t="s">
+      <c r="AY19" t="s">
+        <v>112</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE19" t="s">
         <v>106</v>
       </c>
-      <c r="AX19" t="s">
-        <v>107</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD19" t="s">
+      <c r="BJ19" t="s">
+        <v>117</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>118</v>
+      </c>
+      <c r="BP19" t="s">
+        <v>109</v>
+      </c>
+      <c r="BQ19" t="s">
+        <v>110</v>
+      </c>
+      <c r="BV19" t="s">
+        <v>111</v>
+      </c>
+      <c r="BW19" t="s">
         <v>112</v>
       </c>
-      <c r="BE19" t="s">
-        <v>102</v>
-      </c>
-      <c r="BJ19" t="s">
-        <v>113</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>114</v>
-      </c>
-      <c r="BP19" t="s">
-        <v>105</v>
-      </c>
-      <c r="BQ19" t="s">
+      <c r="CB19" t="s">
+        <v>119</v>
+      </c>
+      <c r="CC19" t="s">
         <v>106</v>
       </c>
-      <c r="BV19" t="s">
-        <v>107</v>
-      </c>
-      <c r="BW19" t="s">
-        <v>108</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>115</v>
-      </c>
-      <c r="CC19" t="s">
-        <v>102</v>
-      </c>
       <c r="CH19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="CI19" t="s">
+        <v>121</v>
+      </c>
+      <c r="CN19" t="s">
+        <v>109</v>
+      </c>
+      <c r="CO19" t="s">
+        <v>110</v>
+      </c>
+      <c r="CT19" t="s">
         <v>111</v>
       </c>
-      <c r="CN19" t="s">
-        <v>105</v>
-      </c>
-      <c r="CO19" t="s">
-        <v>106</v>
-      </c>
-      <c r="CT19" t="s">
-        <v>107</v>
-      </c>
       <c r="CU19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:100">
       <c r="B20" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H20" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I20" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="N20" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="O20" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="T20" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="U20" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="Z20" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG20" t="s">
         <v>125</v>
       </c>
-      <c r="AA20" t="s">
-        <v>126</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>127</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>120</v>
-      </c>
       <c r="AL20" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR20" t="s">
         <v>128</v>
       </c>
-      <c r="AM20" t="s">
+      <c r="AS20" t="s">
         <v>129</v>
       </c>
-      <c r="AR20" t="s">
-        <v>123</v>
-      </c>
-      <c r="AS20" t="s">
-        <v>124</v>
-      </c>
       <c r="AX20" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE20" t="s">
         <v>125</v>
       </c>
-      <c r="AY20" t="s">
-        <v>126</v>
-      </c>
-      <c r="BD20" t="s">
+      <c r="BJ20" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>137</v>
+      </c>
+      <c r="BP20" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ20" t="s">
+        <v>129</v>
+      </c>
+      <c r="BV20" t="s">
         <v>130</v>
       </c>
-      <c r="BE20" t="s">
-        <v>120</v>
-      </c>
-      <c r="BJ20" t="s">
+      <c r="BW20" t="s">
         <v>131</v>
       </c>
-      <c r="BK20" t="s">
-        <v>132</v>
-      </c>
-      <c r="BP20" t="s">
-        <v>123</v>
-      </c>
-      <c r="BQ20" t="s">
-        <v>124</v>
-      </c>
-      <c r="BV20" t="s">
+      <c r="CB20" t="s">
+        <v>138</v>
+      </c>
+      <c r="CC20" t="s">
         <v>125</v>
       </c>
-      <c r="BW20" t="s">
-        <v>126</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>133</v>
-      </c>
-      <c r="CC20" t="s">
-        <v>120</v>
-      </c>
       <c r="CH20" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="CI20" t="s">
+        <v>140</v>
+      </c>
+      <c r="CN20" t="s">
+        <v>128</v>
+      </c>
+      <c r="CO20" t="s">
         <v>129</v>
       </c>
-      <c r="CN20" t="s">
-        <v>123</v>
-      </c>
-      <c r="CO20" t="s">
-        <v>124</v>
-      </c>
       <c r="CT20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="CU20" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:100">
       <c r="T21" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="U21" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="Z21" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AA21" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AR21" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AS21" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="AX21" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AY21" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BP21" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="BQ21" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="BV21" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="BW21" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="CN21" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="CO21" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="CT21" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="CU21" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:100">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AE22" t="s">
-        <v>139</v>
-      </c>
-      <c r="AF22"/>
-      <c r="AG22"/>
+        <v>145</v>
+      </c>
       <c r="AK22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BC22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BI22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CA22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CG22" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:100">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="M23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="S23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Y23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AE23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AK23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AQ23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AW23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BC23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="BI23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="BO23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BU23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CA23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="CG23" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="CM23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CS23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:100">
       <c r="B24" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="H24" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J24" t="s">
+        <v>152</v>
+      </c>
+      <c r="N24" t="s">
+        <v>153</v>
+      </c>
+      <c r="O24" t="s">
+        <v>154</v>
+      </c>
+      <c r="P24" t="s">
+        <v>155</v>
+      </c>
+      <c r="S24" t="s">
         <v>146</v>
       </c>
-      <c r="N24" t="s">
-        <v>147</v>
-      </c>
-      <c r="O24" t="s">
-        <v>148</v>
-      </c>
-      <c r="P24" t="s">
-        <v>149</v>
-      </c>
-      <c r="S24" t="s">
-        <v>140</v>
-      </c>
       <c r="Y24" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AF24" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AG24" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>159</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>160</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>146</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>146</v>
+      </c>
+      <c r="BD24" t="s">
         <v>150</v>
       </c>
-      <c r="AH24" t="s">
+      <c r="BE24" t="s">
+        <v>156</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>152</v>
+      </c>
+      <c r="BJ24" t="s">
+        <v>161</v>
+      </c>
+      <c r="BK24" t="s">
+        <v>162</v>
+      </c>
+      <c r="BL24" t="s">
+        <v>163</v>
+      </c>
+      <c r="BO24" t="s">
+        <v>146</v>
+      </c>
+      <c r="BU24" t="s">
+        <v>146</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>150</v>
+      </c>
+      <c r="CC24" t="s">
         <v>151</v>
       </c>
-      <c r="AL24" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>153</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>154</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>140</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>140</v>
-      </c>
-      <c r="BD24" t="s">
-        <v>144</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>150</v>
-      </c>
-      <c r="BF24" t="s">
+      <c r="CD24" t="s">
+        <v>157</v>
+      </c>
+      <c r="CH24" t="s">
+        <v>164</v>
+      </c>
+      <c r="CI24" t="s">
+        <v>165</v>
+      </c>
+      <c r="CJ24" t="s">
+        <v>166</v>
+      </c>
+      <c r="CM24" t="s">
         <v>146</v>
       </c>
-      <c r="BJ24" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK24" t="s">
-        <v>156</v>
-      </c>
-      <c r="BL24" t="s">
-        <v>157</v>
-      </c>
-      <c r="BO24" t="s">
-        <v>140</v>
-      </c>
-      <c r="BU24" t="s">
-        <v>140</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>144</v>
-      </c>
-      <c r="CC24" t="s">
-        <v>145</v>
-      </c>
-      <c r="CD24" t="s">
-        <v>151</v>
-      </c>
-      <c r="CH24" t="s">
-        <v>152</v>
-      </c>
-      <c r="CI24" t="s">
-        <v>153</v>
-      </c>
-      <c r="CJ24" t="s">
-        <v>154</v>
-      </c>
-      <c r="CM24" t="s">
-        <v>140</v>
-      </c>
       <c r="CS24" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:100">
       <c r="B25" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I25" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="J25" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="N25" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="O25" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="P25" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="T25" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="U25" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="V25" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="Z25" t="s">
+        <v>179</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>172</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>182</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>183</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>176</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>178</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>179</v>
+      </c>
+      <c r="AY25" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ25" t="s">
+        <v>180</v>
+      </c>
+      <c r="BD25" t="s">
+        <v>181</v>
+      </c>
+      <c r="BE25" t="s">
+        <v>171</v>
+      </c>
+      <c r="BF25" t="s">
+        <v>185</v>
+      </c>
+      <c r="BJ25" t="s">
+        <v>186</v>
+      </c>
+      <c r="BK25" t="s">
+        <v>187</v>
+      </c>
+      <c r="BL25" t="s">
+        <v>188</v>
+      </c>
+      <c r="BP25" t="s">
+        <v>176</v>
+      </c>
+      <c r="BQ25" t="s">
+        <v>177</v>
+      </c>
+      <c r="BR25" t="s">
+        <v>178</v>
+      </c>
+      <c r="BV25" t="s">
+        <v>179</v>
+      </c>
+      <c r="BW25" t="s">
+        <v>177</v>
+      </c>
+      <c r="BX25" t="s">
+        <v>180</v>
+      </c>
+      <c r="CB25" t="s">
         <v>170</v>
       </c>
-      <c r="AA25" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB25" t="s">
+      <c r="CC25" t="s">
         <v>171</v>
       </c>
-      <c r="AF25" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>162</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>163</v>
-      </c>
-      <c r="AL25" t="s">
-        <v>173</v>
-      </c>
-      <c r="AM25" t="s">
-        <v>174</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>175</v>
-      </c>
-      <c r="AR25" t="s">
-        <v>167</v>
-      </c>
-      <c r="AS25" t="s">
-        <v>168</v>
-      </c>
-      <c r="AT25" t="s">
-        <v>169</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>170</v>
-      </c>
-      <c r="AY25" t="s">
-        <v>168</v>
-      </c>
-      <c r="AZ25" t="s">
-        <v>171</v>
-      </c>
-      <c r="BD25" t="s">
-        <v>172</v>
-      </c>
-      <c r="BE25" t="s">
-        <v>162</v>
-      </c>
-      <c r="BF25" t="s">
+      <c r="CD25" t="s">
+        <v>185</v>
+      </c>
+      <c r="CH25" t="s">
+        <v>189</v>
+      </c>
+      <c r="CI25" t="s">
+        <v>190</v>
+      </c>
+      <c r="CJ25" t="s">
+        <v>191</v>
+      </c>
+      <c r="CN25" t="s">
         <v>176</v>
       </c>
-      <c r="BJ25" t="s">
+      <c r="CO25" t="s">
         <v>177</v>
       </c>
-      <c r="BK25" t="s">
+      <c r="CP25" t="s">
         <v>178</v>
       </c>
-      <c r="BL25" t="s">
+      <c r="CT25" t="s">
         <v>179</v>
       </c>
-      <c r="BP25" t="s">
-        <v>167</v>
-      </c>
-      <c r="BQ25" t="s">
-        <v>168</v>
-      </c>
-      <c r="BR25" t="s">
-        <v>169</v>
-      </c>
-      <c r="BV25" t="s">
-        <v>170</v>
-      </c>
-      <c r="BW25" t="s">
-        <v>168</v>
-      </c>
-      <c r="BX25" t="s">
-        <v>171</v>
-      </c>
-      <c r="CB25" t="s">
-        <v>161</v>
-      </c>
-      <c r="CC25" t="s">
-        <v>162</v>
-      </c>
-      <c r="CD25" t="s">
-        <v>176</v>
-      </c>
-      <c r="CH25" t="s">
-        <v>173</v>
-      </c>
-      <c r="CI25" t="s">
-        <v>174</v>
-      </c>
-      <c r="CJ25" t="s">
-        <v>175</v>
-      </c>
-      <c r="CN25" t="s">
-        <v>167</v>
-      </c>
-      <c r="CO25" t="s">
-        <v>168</v>
-      </c>
-      <c r="CP25" t="s">
-        <v>169</v>
-      </c>
-      <c r="CT25" t="s">
-        <v>170</v>
-      </c>
       <c r="CU25" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="CV25" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:100">
       <c r="B26" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="H26" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="I26" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="J26" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="N26" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="O26" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="P26" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="T26" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="U26" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="V26" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="Z26" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="AA26" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="AB26" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="AF26" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AG26" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AH26" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="AL26" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>208</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>209</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>201</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>202</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>203</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>201</v>
+      </c>
+      <c r="AY26" t="s">
+        <v>204</v>
+      </c>
+      <c r="AZ26" t="s">
+        <v>205</v>
+      </c>
+      <c r="BD26" t="s">
         <v>195</v>
       </c>
-      <c r="AM26" t="s">
-        <v>196</v>
-      </c>
-      <c r="AN26" t="s">
+      <c r="BE26" t="s">
+        <v>210</v>
+      </c>
+      <c r="BF26" t="s">
         <v>197</v>
       </c>
-      <c r="AR26" t="s">
-        <v>189</v>
-      </c>
-      <c r="AS26" t="s">
-        <v>190</v>
-      </c>
-      <c r="AT26" t="s">
-        <v>191</v>
-      </c>
-      <c r="AX26" t="s">
-        <v>189</v>
-      </c>
-      <c r="AY26" t="s">
-        <v>192</v>
-      </c>
-      <c r="AZ26" t="s">
-        <v>193</v>
-      </c>
-      <c r="BD26" t="s">
-        <v>183</v>
-      </c>
-      <c r="BE26" t="s">
-        <v>198</v>
-      </c>
-      <c r="BF26" t="s">
-        <v>185</v>
-      </c>
       <c r="BJ26" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="BK26" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="BL26" t="s">
+        <v>213</v>
+      </c>
+      <c r="BP26" t="s">
         <v>201</v>
       </c>
-      <c r="BP26" t="s">
-        <v>189</v>
-      </c>
       <c r="BQ26" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="BR26" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="BV26" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="BW26" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="BX26" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="CB26" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="CC26" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="CD26" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="CH26" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="CI26" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="CJ26" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="CN26" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="CO26" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="CP26" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="CT26" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="CU26" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="CV26" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:100">
       <c r="T27" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="U27" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="V27" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="Z27" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="AA27" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="AB27" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="AR27" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="AS27" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="AT27" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AX27" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="AY27" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="AZ27" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="BP27" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="BQ27" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="BR27" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="BV27" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="BW27" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="BX27" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="CN27" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="CO27" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="CP27" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="CT27" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="CU27" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="CV27" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:100">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="M28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AE28" t="s">
-        <v>139</v>
-      </c>
-      <c r="AF28"/>
-      <c r="AG28"/>
-      <c r="AH28"/>
+        <v>145</v>
+      </c>
       <c r="AK28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BC28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BI28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CA28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CG28" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:100">
       <c r="A29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="G29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="M29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="S29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="Y29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AE29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="AK29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="AQ29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AW29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BC29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="BI29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="BO29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="BU29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CA29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="CG29" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="CM29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="CS29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:100">
       <c r="B30" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C30" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="D30" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="H30" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="I30" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="J30" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="N30" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="O30" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="P30" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="S30" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="Y30" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="AF30" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="AG30" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="AH30" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="AL30" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="AM30" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="AN30" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="AQ30" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="AW30" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="BD30" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="BE30" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="BF30" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="BJ30" t="s">
+        <v>238</v>
+      </c>
+      <c r="BK30" t="s">
+        <v>239</v>
+      </c>
+      <c r="BL30" t="s">
+        <v>240</v>
+      </c>
+      <c r="BO30" t="s">
         <v>223</v>
       </c>
-      <c r="BK30" t="s">
-        <v>224</v>
-      </c>
-      <c r="BL30" t="s">
-        <v>225</v>
-      </c>
-      <c r="BO30" t="s">
-        <v>208</v>
-      </c>
       <c r="BU30" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="CB30" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="CC30" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="CD30" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="CH30" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="CI30" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="CJ30" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="CM30" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="CS30" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:100">
       <c r="B31" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="D31" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="H31" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="I31" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="J31" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="N31" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="O31" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="P31" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="T31" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="U31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="V31" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="Z31" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="AA31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="AB31" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="AF31" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="AH31" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="AL31" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="AM31" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="AN31" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="AR31" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="AS31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="AT31" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="AX31" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="AY31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="AZ31" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="BD31" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="BE31" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="BF31" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="BJ31" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="BK31" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="BL31" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="BP31" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="BQ31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="BR31" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="BV31" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="BW31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="BX31" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="CB31" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="CC31" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="CD31" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="CH31" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="CI31" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="CJ31" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="CN31" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="CO31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="CP31" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="CT31" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="CU31" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="CV31" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:100">
       <c r="B32" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C32" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="D32" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="H32" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="I32" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="J32" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="O32" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="T32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="U32" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="V32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="Z32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="AA32" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AB32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="AF32" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AH32" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AM32" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="AR32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="AS32" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="AT32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="AX32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="AY32" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="AZ32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="BD32" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="BE32" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="BF32" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="BJ32" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="BK32" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="BL32" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="BP32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="BQ32" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="BR32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="BV32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="BW32" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="BX32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="CB32" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="CC32" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="CD32" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="CH32" t="s">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="CI32" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="CJ32" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="CN32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="CO32" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="CP32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="CT32" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="CU32" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="CV32" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:100">
       <c r="T33" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="U33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="V33" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="Z33" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AA33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="AB33" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="AR33" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="AS33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="AT33" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="AX33" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AY33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="AZ33" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="BP33" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="BQ33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="BR33" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="BV33" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="BW33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="BX33" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="CN33" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="CO33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="CP33" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="CT33" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="CU33" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="CV33" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:100">
       <c r="A34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="G34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="M34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="AE34" t="s">
-        <v>272</v>
-      </c>
-      <c r="AF34"/>
-      <c r="AG34"/>
-      <c r="AH34"/>
+        <v>295</v>
+      </c>
       <c r="AK34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="BC34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="BI34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="CA34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="CG34" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:100">
       <c r="B35" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="H35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="N35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="AF35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="AL35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="BD35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="BJ35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="CB35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="CH35" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:100">
       <c r="B36" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="N36" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="AL36" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="BJ36" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="CH36" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:100">
       <c r="B37" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="N37" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="BJ37" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="CH37" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:100">
       <c r="B38" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:100">
       <c r="B39" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:100">
       <c r="B40" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:100">
       <c r="B41" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
